--- a/trading_signals/risk_management/risk_workbook_20260618_000000.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260618_000000.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -147,10 +147,10 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,22 +184,22 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,6 +212,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -351,12 +357,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'NAV Trend'!$A$4:$A$161</f>
+              <f>'NAV Trend'!$A$4:$A$160</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'NAV Trend'!$B$4:$B$161</f>
+              <f>'NAV Trend'!$B$4:$B$160</f>
             </numRef>
           </val>
         </ser>
@@ -728,7 +734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-18  ·  Generated 2026-06-24T21:37:00  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-17  ·  Generated 2026-06-25T01:50:13  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +745,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +755,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.034</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="6">
@@ -758,8 +764,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0.356</v>
+      <c r="B6" s="5" t="n">
+        <v>0.355</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +775,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.978</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +785,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22560.28</v>
+        <v>22944.33</v>
       </c>
     </row>
     <row r="9">
@@ -788,8 +794,8 @@
           <t>VaR 95% 1-day (% NAV)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>1.99</v>
+      <c r="B9" s="6" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="10">
@@ -798,8 +804,8 @@
           <t>Annual vol (% NAV)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>19.19</v>
+      <c r="B10" s="6" t="n">
+        <v>19.66</v>
       </c>
     </row>
     <row r="11">
@@ -808,8 +814,8 @@
           <t>Sharpe (annual)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>1.489</v>
+      <c r="B11" s="6" t="n">
+        <v>1.445</v>
       </c>
     </row>
     <row r="12">
@@ -818,8 +824,8 @@
           <t>PSR( SR&gt;0 )</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>0.8823</v>
+      <c r="B12" s="5" t="n">
+        <v>0.8747</v>
       </c>
     </row>
     <row r="13">
@@ -828,7 +834,7 @@
           <t>CDaR 95% (%)</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>8.859999999999999</v>
       </c>
     </row>
@@ -840,7 +846,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>5.26 / 2.63</t>
+          <t>5.07 / 2.54</t>
         </is>
       </c>
     </row>
@@ -851,7 +857,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.034</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +868,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMAT (16.15% NAV)</t>
+          <t>AMAT (16.27% NAV)</t>
         </is>
       </c>
     </row>
@@ -872,8 +878,8 @@
           <t>Max sector net (% gross)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>34.88</v>
+      <c r="B17" s="6" t="n">
+        <v>38.19</v>
       </c>
     </row>
     <row r="18">
@@ -882,8 +888,8 @@
           <t>Open pairs</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>7</v>
+      <c r="B18" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -892,8 +898,8 @@
           <t>Limit breaches</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>6</v>
+      <c r="B19" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -944,7 +950,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>22560.28</v>
+        <v>22944.33</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +960,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>31899.82</v>
+        <v>32442.87</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +970,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>217710.22</v>
+        <v>221416.41</v>
       </c>
     </row>
     <row r="6">
@@ -973,8 +979,8 @@
           <t>Annual vol (% NAV)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>19.19</v>
+      <c r="B6" s="6" t="n">
+        <v>19.66</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +990,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10165.43</v>
+        <v>11738.61</v>
       </c>
     </row>
     <row r="8">
@@ -994,11 +1000,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22115.32</v>
+        <v>22781.28</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>COMPONENT VaR (per pair, marginal)</t>
         </is>
@@ -1028,10 +1034,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>7662.29</v>
+        <v>7731.48</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>33.96</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="13">
@@ -1041,10 +1047,10 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>7487.22</v>
+        <v>7588.85</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>33.19</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="14">
@@ -1054,10 +1060,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3804.3</v>
+        <v>3851.06</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>16.86</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="15">
@@ -1067,10 +1073,10 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>2142.4</v>
+        <v>2033.88</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1080,10 +1086,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1497.67</v>
+        <v>1638.78</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>6.64</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="17">
@@ -1093,23 +1099,10 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>123.98</v>
+        <v>100.28</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>AON/KKR</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="n">
-        <v>-157.58</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>-0.7</v>
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -1126,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1189,10 +1182,10 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>525</v>
+        <v>578</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1209030</v>
+        <v>1132306</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
@@ -1210,10 +1203,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>3004</v>
+        <v>3311</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>5349685</v>
+        <v>5226987</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>0</v>
@@ -1222,19 +1215,19 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>AON/KKR</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>226</v>
+        <v>670</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1563564</v>
+        <v>6476364</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1243,19 +1236,19 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>AON/KKR</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>767</v>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>4308372</v>
+        <v>1127224</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>0</v>
@@ -1264,19 +1257,19 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>670</v>
+        <v>386</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7740012</v>
+        <v>1125856</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1285,19 +1278,19 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>23</v>
+          <t>STLD/UHS</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>358</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>1221275</v>
+        <v>1002137</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>0</v>
@@ -1306,19 +1299,19 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1305499</v>
+        <v>8835886</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1327,19 +1320,19 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>358</v>
+        <v>1466</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>1056905</v>
+        <v>2904350</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>0</v>
@@ -1348,19 +1341,19 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8835886</v>
+        <v>10458954</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1369,19 +1362,19 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>1466</v>
+        <v>395</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>3255332</v>
+        <v>2402636</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>0</v>
@@ -1390,19 +1383,19 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>269</v>
+        <v>394</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10458954</v>
+        <v>1936716</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1411,63 +1404,21 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>2402636</v>
+        <v>38900737</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>ODFL</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>ODFL/PLTR</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>394</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1936716</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/PLTR</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>372</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>38900737</v>
-      </c>
-      <c r="E19" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1523,11 +1474,11 @@
           <t>SPY -5%</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>-55472.32</v>
-      </c>
-      <c r="C4" s="23" t="n">
-        <v>-4.89</v>
+      <c r="B4" s="28" t="n">
+        <v>-57542.9</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>-5.11</v>
       </c>
     </row>
     <row r="5">
@@ -1536,11 +1487,11 @@
           <t>SPY -10%</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>-110944.64</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>-9.779999999999999</v>
+      <c r="B5" s="29" t="n">
+        <v>-115085.8</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>-10.22</v>
       </c>
     </row>
     <row r="6">
@@ -1549,11 +1500,11 @@
           <t>VIX +10pt</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>-55472.32</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <v>-4.89</v>
+      <c r="B6" s="28" t="n">
+        <v>-57542.9</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>-5.11</v>
       </c>
     </row>
     <row r="7">
@@ -1562,11 +1513,11 @@
           <t>Top sector -10%</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>-40917.75</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>-3.61</v>
+      <c r="B7" s="29" t="n">
+        <v>-39522.14</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>-3.51</v>
       </c>
     </row>
   </sheetData>
@@ -1634,130 +1585,130 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>gross_leverage</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>mrpt</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="D4" s="30" t="n">
+      <c r="C4" s="32" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D4" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>net_leverage_abs</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>mrpt</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="30" t="n">
+      <c r="C5" s="32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D5" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>gross_leverage</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>mtfs</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="32" t="n">
         <v>1.58</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>net_leverage_abs</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>mtfs</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="34" t="n">
         <v>0.72</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="34" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>amber</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>single_name_gross</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>AMAT</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="D8" s="32" t="n">
+      <c r="C8" s="34" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="D8" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>amber</t>
         </is>
@@ -1775,7 +1726,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>15.33</v>
+        <v>14.2</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1785,183 +1736,183 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>single_name_gross</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>sector_net</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
           <t>amber</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>single_name_gross</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="F10" s="30" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>max_pair</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>net_market_beta</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>var_95_1d</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>sector_net</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="D11" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>max_pair</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="n">
-        <v>21.76</v>
-      </c>
-      <c r="D12" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>net_market_beta</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E13" s="34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="34" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>var_95_1d</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="D14" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="30" t="n">
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>open_pairs</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>mrpt</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>open_pairs</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>mtfs</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>open_pairs</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>mrpt</t>
-        </is>
-      </c>
-      <c r="C15" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="30" t="n">
+      <c r="D16" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>open_pairs</t>
-        </is>
-      </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>mtfs</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -1981,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2077,13 +2028,13 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>525</v>
+        <v>578</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>145.33</v>
+        <v>143.92</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>76298.25</v>
+        <v>83185.75999999999</v>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
@@ -2121,13 +2072,13 @@
         </is>
       </c>
       <c r="E5" s="24" t="n">
-        <v>-3004</v>
+        <v>-3311</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>-73057.28</v>
+        <v>24.33</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>-80556.63</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -2146,17 +2097,17 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>AON/KKR</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -2165,17 +2116,17 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>226</v>
+        <v>670</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>317.74</v>
+        <v>238.73</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>71809.24000000001</v>
+        <v>159949.1</v>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I6" s="16" t="n">
@@ -2183,24 +2134,24 @@
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>fast_signal_tight_stop</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>AON/KKR</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2209,17 +2160,17 @@
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-767</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>97.01000000000001</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>-74406.67</v>
+        <v>-23</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>607.9299999999999</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>-13982.39</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -2227,7 +2178,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>fast_signal_tight_stop</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2190,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -2253,25 +2204,25 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>670</v>
+        <v>386</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>259.56</v>
+        <v>270.13</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>173905.2</v>
+        <v>104270.18</v>
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="I8" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
     </row>
@@ -2283,12 +2234,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2297,13 +2248,13 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-23</v>
+        <v>-358</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>609.9400000000001</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>-14028.62</v>
+        <v>141.26</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>-50571.08</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -2311,11 +2262,11 @@
         </is>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2278,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -2341,25 +2292,25 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>249.91</v>
+        <v>592.92</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>96465.25999999999</v>
+        <v>183212.28</v>
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I10" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2322,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2385,25 +2336,25 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-358</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>141.17</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>-50538.86</v>
+        <v>-1466</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>-71643.42</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2415,12 +2366,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -2429,13 +2380,13 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>592.92</v>
+        <v>374.18</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>183212.28</v>
+        <v>100654.42</v>
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
@@ -2447,7 +2398,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>let_profits_run</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2410,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2473,17 +2424,17 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-1466</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>-72068.56</v>
+        <v>-395</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>132.13</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>-52191.35</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
@@ -2491,7 +2442,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>let_profits_run</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2454,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -2517,17 +2468,17 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>269</v>
+        <v>394</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>374.18</v>
+        <v>218.36</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>100654.42</v>
+        <v>86033.84</v>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="I14" s="16" t="n">
@@ -2535,7 +2486,7 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2498,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2561,111 +2512,23 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-395</v>
+        <v>-372</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>132.13</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>-52191.35</v>
+        <v>130.63</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>-48594.36</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>let_profits_run</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/PLTR</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>ODFL</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>394</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>218.36</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>86033.84</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>industrial</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>weekly_aligned_windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>ODFL/PLTR</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>-372</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>130.63</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>-48594.36</v>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -2685,7 +2548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2752,11 +2615,11 @@
           <t>EXR/WY</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
-        <v>770.29</v>
+      <c r="C4" s="14" t="n">
+        <v>89.62</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>149355.53</v>
+        <v>163742.39</v>
       </c>
       <c r="E4" s="16" t="n">
         <v>0</v>
@@ -2775,26 +2638,26 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>AON/KKR</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>-1899.98</v>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>25799.84</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>146215.91</v>
+        <v>173931.49</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>fast_signal_tight_stop</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -2811,21 +2674,21 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>39709.71</v>
+        <v>1957.36</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>187933.82</v>
+        <v>154841.26</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
@@ -2842,21 +2705,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>-5815.34</v>
+          <t>AMAT/TRMB</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>14103.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>147004.12</v>
+        <v>254855.7</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2873,21 +2736,21 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>13677.96</v>
+          <t>LRCX/NRG</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>-193.31</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>255280.84</v>
+        <v>152845.77</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>let_profits_run</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -2904,55 +2767,24 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>-193.31</v>
+          <t>ODFL/PLTR</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>-11416.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>152845.77</v>
+        <v>134628.2</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/PLTR</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>-11416.2</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>134628.2</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>weekly_aligned_windows</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3012,12 +2844,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
@@ -3029,12 +2861,12 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -3046,12 +2878,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -3086,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3111,7 +2943,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>MASTER (4 strategies) — 等资本 vs 等风险</t>
         </is>
@@ -3151,16 +2983,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.05</v>
+        <v>14.44</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.44</v>
+        <v>0.33</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="23" t="n">
-        <v>-13.61</v>
+      <c r="E6" s="21" t="n">
+        <v>-14.11</v>
       </c>
     </row>
     <row r="7">
@@ -3170,16 +3002,16 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>13.56</v>
+        <v>13.87</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>24.5</v>
+        <v>25.68</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="20" t="n">
-        <v>10.94</v>
+      <c r="E7" s="19" t="n">
+        <v>11.81</v>
       </c>
     </row>
     <row r="8">
@@ -3189,16 +3021,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>23.39</v>
+        <v>24.16</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="23" t="n">
-        <v>-20.15</v>
+      <c r="E8" s="21" t="n">
+        <v>-20.6</v>
       </c>
     </row>
     <row r="9">
@@ -3208,20 +3040,20 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>49</v>
+        <v>47.53</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>71.81</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>22.81</v>
+      <c r="E9" s="19" t="n">
+        <v>22.9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>PAIRS (within combined book)</t>
         </is>
@@ -3246,7 +3078,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>33.96</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="14">
@@ -3256,7 +3088,7 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>33.19</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="15">
@@ -3266,7 +3098,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>16.86</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="16">
@@ -3276,7 +3108,7 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3286,7 +3118,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>6.64</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="18">
@@ -3296,17 +3128,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>AON/KKR</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>-0.7</v>
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -3416,7 +3238,7 @@
           <t>COMBINED</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="20" t="n">
         <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
@@ -3465,7 +3287,7 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="19" t="n">
         <v>47.74</v>
       </c>
       <c r="C6" s="16" t="n">
@@ -3514,7 +3336,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="20" t="n">
         <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
@@ -3642,10 +3464,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.802</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>20.709</v>
+        <v>20.611</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -3654,10 +3476,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.384</v>
+        <v>2.395</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.384</v>
+        <v>2.395</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -3670,10 +3492,10 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>-0.446</v>
+        <v>-0.437</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>2.668</v>
+        <v>2.64</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0</v>
@@ -3682,13 +3504,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>1.561</v>
+        <v>1.569</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>1.631</v>
+        <v>1.636</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="6">
@@ -3698,10 +3520,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.908</v>
+        <v>1.907</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>23.781</v>
+        <v>23.64</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -3710,10 +3532,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5.128</v>
+        <v>5.15</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>5.128</v>
+        <v>5.15</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -3778,13 +3600,13 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.489</v>
+        <v>1.445</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8823</v>
+        <v>0.8747</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>8.859999999999999</v>
@@ -3793,16 +3615,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>5.26</v>
+        <v>5.07</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.034</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="10">
@@ -3812,13 +3634,13 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>1.346</v>
+        <v>1.301</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.8497</v>
+        <v>0.8411</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>9.35</v>
@@ -3827,16 +3649,16 @@
         <v>9.57</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>6.49</v>
+        <v>6.2</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.512</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="11">
@@ -3846,13 +3668,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.183</v>
+        <v>1.156</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.8377</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -3861,16 +3683,16 @@
         <v>18.48</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.576</v>
+        <v>1.579</v>
       </c>
     </row>
   </sheetData>
@@ -3945,16 +3767,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>338327.1</v>
+        <v>402427.78</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>403954.02</v>
+        <v>252416.46</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>196753.26</v>
+        <v>167616.4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>370128.88</v>
+        <v>562974.8199999999</v>
       </c>
     </row>
     <row r="6">
@@ -3964,16 +3786,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>392583.41</v>
+        <v>323890.01</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>331500.67</v>
+        <v>348325.82</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>416204.88</v>
+        <v>463736.55</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>660410.59</v>
+        <v>431436.49</v>
       </c>
     </row>
     <row r="7">
@@ -3983,16 +3805,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>788378.49</v>
+        <v>717305.58</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>715630.11</v>
+        <v>861795.75</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>931014.58</v>
+        <v>877838.04</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>631213.7</v>
+        <v>426885.9</v>
       </c>
     </row>
     <row r="8">
@@ -4002,16 +3824,16 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1519289</v>
+        <v>1443623.37</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>1451084.8</v>
+        <v>1462538.03</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1543972.72</v>
+        <v>1509190.99</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1661753.17</v>
+        <v>1421297.21</v>
       </c>
     </row>
     <row r="9">
@@ -4021,16 +3843,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>384885.7</v>
+        <v>317539.23</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>325000.66</v>
+        <v>341495.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>408044</v>
+        <v>454643.68</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>647461.36</v>
+        <v>422976.95</v>
       </c>
     </row>
     <row r="10">
@@ -4059,16 +3881,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>384885.7</v>
+        <v>317539.23</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>325000.66</v>
+        <v>341495.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>408044</v>
+        <v>454643.68</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>647461.36</v>
+        <v>422976.95</v>
       </c>
     </row>
     <row r="12">
@@ -4078,16 +3900,16 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1135928.72</v>
+        <v>1054547.31</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>1014291.81</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="13">
@@ -4097,16 +3919,16 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1.034</v>
+        <v>0.919</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0.924</v>
+        <v>1.073</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.179</v>
+        <v>1.264</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.261</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="14">
@@ -4116,16 +3938,16 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>0.347</v>
+        <v>0.464</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.46</v>
+        <v>0.401</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.016</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="15">
@@ -4135,16 +3957,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>234652.84</v>
+        <v>206968.96</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>208126.15</v>
+        <v>240658.33</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>267811.72</v>
+        <v>266496.34</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>255735.01</v>
+        <v>169972.57</v>
       </c>
     </row>
     <row r="16">
@@ -4154,16 +3976,16 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>899750.46</v>
+        <v>919115.1800000001</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>917957.99</v>
+        <v>880383.8</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>868117</v>
+        <v>788050.97</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>758556.8</v>
+        <v>828347.6899999999</v>
       </c>
     </row>
     <row r="17">
@@ -4173,16 +3995,16 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
         <v>-0</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4226,16 +4048,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>788378.49</v>
+        <v>717305.58</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>715630.11</v>
+        <v>861795.75</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>931014.58</v>
+        <v>877838.04</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>631213.7</v>
+        <v>426885.9</v>
       </c>
     </row>
     <row r="22">
@@ -4264,16 +4086,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>788378.49</v>
+        <v>717305.58</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>715630.11</v>
+        <v>861795.75</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>931014.58</v>
+        <v>877838.04</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>631213.7</v>
+        <v>426885.9</v>
       </c>
     </row>
     <row r="24">
@@ -4302,16 +4124,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>788378.49</v>
+        <v>717305.58</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>715630.11</v>
+        <v>861795.75</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>931014.58</v>
+        <v>877838.04</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>631213.7</v>
+        <v>426885.9</v>
       </c>
     </row>
     <row r="26">
@@ -4321,16 +4143,16 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>7697.71</v>
+        <v>6350.78</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>6500.01</v>
+        <v>6829.92</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>8160.88</v>
+        <v>9092.870000000001</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>12949.23</v>
+        <v>8459.540000000001</v>
       </c>
     </row>
     <row r="27">
@@ -4340,16 +4162,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>7697.71</v>
+        <v>6350.78</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>6500.01</v>
+        <v>6829.92</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8160.88</v>
+        <v>9092.870000000001</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>12949.23</v>
+        <v>8459.540000000001</v>
       </c>
     </row>
     <row r="28">
@@ -4359,16 +4181,16 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>384885.7</v>
+        <v>317539.23</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>325000.66</v>
+        <v>341495.9</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>408044</v>
+        <v>454643.68</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>647461.36</v>
+        <v>422976.95</v>
       </c>
     </row>
     <row r="29">
@@ -4378,16 +4200,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>384885.7</v>
+        <v>317539.23</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>325000.66</v>
+        <v>341495.9</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>408044</v>
+        <v>454643.68</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>647461.36</v>
+        <v>422976.95</v>
       </c>
     </row>
     <row r="30">
@@ -4416,16 +4238,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>7697.71</v>
+        <v>6350.78</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6500.01</v>
+        <v>6829.92</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8160.88</v>
+        <v>9092.870000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>12949.23</v>
+        <v>8459.540000000001</v>
       </c>
     </row>
     <row r="32">
@@ -4435,16 +4257,16 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>338327.1</v>
+        <v>402427.78</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>403954.02</v>
+        <v>252416.46</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>196753.26</v>
+        <v>167616.4</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>370128.88</v>
+        <v>562974.8199999999</v>
       </c>
     </row>
     <row r="33">
@@ -4454,16 +4276,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1135928.72</v>
+        <v>1054547.31</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1014291.81</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="34">
@@ -4526,16 +4348,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>426281.61</v>
+        <v>489721.24</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>488257.34</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>566922.75</v>
+        <v>476743.58</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>270479.53</v>
+        <v>484682.15</v>
       </c>
     </row>
     <row r="40">
@@ -4545,16 +4367,16 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>150413.23</v>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>83721.28</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>0</v>
+        <v>82167.75999999999</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>89048.96000000001</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>321513.39</v>
+        <v>90710.5</v>
       </c>
     </row>
     <row r="41">
@@ -4564,16 +4386,16 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>148107.49</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>84619.2</v>
-      </c>
-      <c r="D41" s="17" t="n">
-        <v>0</v>
+        <v>83185.75999999999</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>87124.84</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>297932.06</v>
+        <v>88136.88</v>
       </c>
     </row>
     <row r="42">
@@ -4583,16 +4405,16 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>724802.33</v>
+        <v>655074.76</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>656597.8199999999</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>566922.75</v>
+        <v>652917.38</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>889924.97</v>
+        <v>663529.54</v>
       </c>
     </row>
     <row r="43">
@@ -4602,16 +4424,16 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>147463.95</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>82079.69</v>
-      </c>
-      <c r="D43" s="17" t="n">
-        <v>0</v>
+        <v>80556.63</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>87302.89999999999</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>315209.2</v>
+        <v>88931.87</v>
       </c>
     </row>
     <row r="44">
@@ -4640,16 +4462,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>147463.95</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>82079.69</v>
-      </c>
-      <c r="D45" s="17" t="n">
-        <v>0</v>
+        <v>80556.63</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>87302.89999999999</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>315209.2</v>
+        <v>88931.87</v>
       </c>
     </row>
     <row r="46">
@@ -4659,16 +4481,16 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>577338.38</v>
+        <v>574518.13</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>566922.75</v>
+        <v>565614.48</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>574715.77</v>
+        <v>574597.67</v>
       </c>
     </row>
     <row r="47">
@@ -4678,16 +4500,16 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.512</v>
+        <v>0.285</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1.067</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="48">
@@ -4697,16 +4519,16 @@
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>-0.03</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="49">
@@ -4716,16 +4538,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>59114.29</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>33339.78</v>
-      </c>
-      <c r="D49" s="17" t="n">
-        <v>0</v>
+        <v>32748.48</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>34885.55</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>122628.25</v>
+        <v>35413.75</v>
       </c>
     </row>
     <row r="50">
@@ -4735,16 +4557,16 @@
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>518224.09</v>
+        <v>541769.65</v>
       </c>
       <c r="C50" s="12" t="n">
-        <v>541178.35</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>566922.75</v>
+        <v>530728.9300000001</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>452087.52</v>
+        <v>539183.92</v>
       </c>
     </row>
     <row r="51">
@@ -4757,10 +4579,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="7" t="n">
         <v>-0</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -4807,16 +4629,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>148107.49</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>84619.2</v>
-      </c>
-      <c r="D55" s="17" t="n">
-        <v>0</v>
+        <v>83185.75999999999</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>87124.84</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>297932.06</v>
+        <v>88136.88</v>
       </c>
     </row>
     <row r="56">
@@ -4845,16 +4667,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>148107.49</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>84619.2</v>
-      </c>
-      <c r="D57" s="17" t="n">
-        <v>0</v>
+        <v>83185.75999999999</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>87124.84</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>297932.06</v>
+        <v>88136.88</v>
       </c>
     </row>
     <row r="58">
@@ -4883,16 +4705,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>148107.49</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>84619.2</v>
-      </c>
-      <c r="D59" s="17" t="n">
-        <v>0</v>
+        <v>83185.75999999999</v>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>87124.84</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>297932.06</v>
+        <v>88136.88</v>
       </c>
     </row>
     <row r="60">
@@ -4902,16 +4724,16 @@
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>2949.28</v>
-      </c>
-      <c r="C60" s="12" t="n">
-        <v>1641.59</v>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>0</v>
+        <v>1611.13</v>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>1746.06</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>6304.18</v>
+        <v>1778.64</v>
       </c>
     </row>
     <row r="61">
@@ -4921,16 +4743,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>2949.28</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>1641.59</v>
-      </c>
-      <c r="D61" s="17" t="n">
-        <v>0</v>
+        <v>1611.13</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1746.06</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6304.18</v>
+        <v>1778.64</v>
       </c>
     </row>
     <row r="62">
@@ -4940,16 +4762,16 @@
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>147463.95</v>
-      </c>
-      <c r="C62" s="12" t="n">
-        <v>82079.69</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>0</v>
+        <v>80556.63</v>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>87302.89999999999</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>315209.2</v>
+        <v>88931.87</v>
       </c>
     </row>
     <row r="63">
@@ -4959,16 +4781,16 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>147463.95</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>82079.69</v>
-      </c>
-      <c r="D63" s="17" t="n">
-        <v>0</v>
+        <v>80556.63</v>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>87302.89999999999</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>315209.2</v>
+        <v>88931.87</v>
       </c>
     </row>
     <row r="64">
@@ -4997,16 +4819,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>2949.28</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>1641.59</v>
-      </c>
-      <c r="D65" s="17" t="n">
-        <v>0</v>
+        <v>1611.13</v>
+      </c>
+      <c r="C65" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>1746.06</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>6304.18</v>
+        <v>1778.64</v>
       </c>
     </row>
     <row r="66">
@@ -5016,16 +4838,16 @@
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>426281.61</v>
+        <v>489721.24</v>
       </c>
       <c r="C66" s="12" t="n">
-        <v>488257.34</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>566922.75</v>
+        <v>476743.58</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>270479.53</v>
+        <v>484682.15</v>
       </c>
     </row>
     <row r="67">
@@ -5035,16 +4857,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>577338.38</v>
+        <v>574518.13</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>566922.75</v>
+        <v>565614.48</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>574715.77</v>
+        <v>574597.67</v>
       </c>
     </row>
     <row r="68">
@@ -5116,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>99649.36</v>
+        <v>78292.67</v>
       </c>
     </row>
     <row r="74">
@@ -5126,16 +4948,16 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>242170.18</v>
+        <v>241722.25</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>247779.39</v>
+        <v>348325.82</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>416204.88</v>
+        <v>374687.6</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>338897.2</v>
+        <v>340725.98</v>
       </c>
     </row>
     <row r="75">
@@ -5145,16 +4967,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>640271</v>
+        <v>634119.8199999999</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>631010.91</v>
+        <v>861795.75</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>931014.58</v>
+        <v>790713.2</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>333281.64</v>
+        <v>338749.02</v>
       </c>
     </row>
     <row r="76">
@@ -5164,16 +4986,16 @@
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>882441.1899999999</v>
+        <v>875842.0699999999</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>878790.3</v>
+        <v>1210121.57</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1347219.46</v>
+        <v>1165400.79</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>771828.2</v>
+        <v>757767.67</v>
       </c>
     </row>
     <row r="77">
@@ -5183,16 +5005,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>237421.75</v>
+        <v>236982.6</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>242920.97</v>
+        <v>341495.9</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>408044</v>
+        <v>367340.78</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>332252.16</v>
+        <v>334045.08</v>
       </c>
     </row>
     <row r="78">
@@ -5202,13 +5024,13 @@
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>87954.50999999999</v>
+        <v>87293.46000000001</v>
       </c>
       <c r="C78" s="12" t="n">
-        <v>84303.32000000001</v>
+        <v>318453.35</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>370169.5</v>
+        <v>309127.18</v>
       </c>
       <c r="E78" s="14" t="n">
         <v>0</v>
@@ -5221,16 +5043,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>325376.26</v>
+        <v>324276.06</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>327224.29</v>
+        <v>659949.25</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>778213.5</v>
+        <v>676467.96</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>332252.16</v>
+        <v>334045.08</v>
       </c>
     </row>
     <row r="80">
@@ -5240,16 +5062,16 @@
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="C80" s="12" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>569005.96</v>
+        <v>488932.83</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>439576.04</v>
+        <v>423722.59</v>
       </c>
     </row>
     <row r="81">
@@ -5259,16 +5081,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>1.576</v>
+        <v>1.579</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>1.584</v>
+        <v>2.187</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>2.353</v>
+        <v>2.369</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1.514</v>
+        <v>1.588</v>
       </c>
     </row>
     <row r="82">
@@ -5278,16 +5100,16 @@
         </is>
       </c>
       <c r="B82" s="16" t="n">
-        <v>0.723</v>
+        <v>0.72</v>
       </c>
       <c r="C82" s="16" t="n">
-        <v>0.704</v>
+        <v>0.946</v>
       </c>
       <c r="D82" s="16" t="n">
-        <v>0.919</v>
+        <v>0.866</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="83">
@@ -5297,16 +5119,16 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>175538.55</v>
+        <v>174220.48</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>174786.38</v>
+        <v>240658.33</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>267811.72</v>
+        <v>231610.8</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>133106.76</v>
+        <v>134558.82</v>
       </c>
     </row>
     <row r="84">
@@ -5316,16 +5138,16 @@
         </is>
       </c>
       <c r="B84" s="12" t="n">
-        <v>381526.37</v>
+        <v>377345.53</v>
       </c>
       <c r="C84" s="12" t="n">
-        <v>376779.63</v>
+        <v>309513.99</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>301194.24</v>
+        <v>257322.03</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>306469.28</v>
+        <v>289163.77</v>
       </c>
     </row>
     <row r="85">
@@ -5338,10 +5160,10 @@
         <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -5388,16 +5210,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>569005.96</v>
+        <v>488932.83</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>333281.64</v>
+        <v>338749.02</v>
       </c>
     </row>
     <row r="90">
@@ -5426,16 +5248,16 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>640271</v>
+        <v>634119.8199999999</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>631010.91</v>
+        <v>861795.75</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>931014.58</v>
+        <v>790713.2</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>333281.64</v>
+        <v>338749.02</v>
       </c>
     </row>
     <row r="92">
@@ -5445,13 +5267,13 @@
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>83206.08</v>
+        <v>82553.81</v>
       </c>
       <c r="C92" s="12" t="n">
-        <v>79444.89999999999</v>
+        <v>311623.43</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>362008.62</v>
+        <v>301780.37</v>
       </c>
       <c r="E92" s="14" t="n">
         <v>0</v>
@@ -5464,16 +5286,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>569005.96</v>
+        <v>488932.83</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>333281.64</v>
+        <v>338749.02</v>
       </c>
     </row>
     <row r="94">
@@ -5492,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>6645.04</v>
+        <v>6680.9</v>
       </c>
     </row>
     <row r="95">
@@ -5511,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>6645.04</v>
+        <v>6680.9</v>
       </c>
     </row>
     <row r="96">
@@ -5521,16 +5343,16 @@
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>237421.75</v>
+        <v>236982.6</v>
       </c>
       <c r="C96" s="12" t="n">
-        <v>242920.97</v>
+        <v>341495.9</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>408044</v>
+        <v>367340.78</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>332252.16</v>
+        <v>334045.08</v>
       </c>
     </row>
     <row r="97">
@@ -5540,16 +5362,16 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>237421.75</v>
+        <v>236982.6</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>242920.97</v>
+        <v>341495.9</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>408044</v>
+        <v>367340.78</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>332252.16</v>
+        <v>334045.08</v>
       </c>
     </row>
     <row r="98">
@@ -5559,13 +5381,13 @@
         </is>
       </c>
       <c r="B98" s="12" t="n">
-        <v>4748.44</v>
+        <v>4739.65</v>
       </c>
       <c r="C98" s="12" t="n">
-        <v>4858.42</v>
+        <v>6829.92</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>8160.88</v>
+        <v>7346.82</v>
       </c>
       <c r="E98" s="14" t="n">
         <v>0</v>
@@ -5587,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>6645.04</v>
+        <v>6680.9</v>
       </c>
     </row>
     <row r="100">
@@ -5606,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>99649.36</v>
+        <v>78292.67</v>
       </c>
     </row>
     <row r="101">
@@ -5616,16 +5438,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>569005.96</v>
+        <v>488932.83</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>439576.04</v>
+        <v>423722.59</v>
       </c>
     </row>
     <row r="102">
@@ -5719,16 +5541,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8319.16</v>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>-1525.42</v>
+        <v>5042.01</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>71536.83</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>120111.49</v>
+        <v>127763.88</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>212904.51</v>
+        <v>204585.35</v>
       </c>
     </row>
     <row r="6">
@@ -5757,7 +5579,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>34833.13</v>
+        <v>30340.41</v>
       </c>
     </row>
     <row r="9">
@@ -5801,16 +5623,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2820.25</v>
+        <v>3648.32</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10415.63</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>2622.61</v>
+        <v>8903.65</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>-79.54000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>68006.44</v>
+        <v>65186.19</v>
       </c>
     </row>
     <row r="12">
@@ -5838,8 +5660,8 @@
           <t>Current unrealized PnL</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
-        <v>-1129.69</v>
+      <c r="B13" s="17" t="n">
+        <v>89.62</v>
       </c>
     </row>
     <row r="15">
@@ -5883,16 +5705,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>5498.91</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>-11941.04</v>
+        <v>1393.69</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>62633.18</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>117488.88</v>
+        <v>127843.42</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>144898.07</v>
+        <v>139399.16</v>
       </c>
     </row>
     <row r="18">
@@ -5902,16 +5724,16 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>12.05</v>
+        <v>11.96</v>
       </c>
       <c r="C18" s="14" t="n">
-        <v>60.24</v>
+        <v>59.79</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>253.02</v>
+        <v>251.12</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>1903.67</v>
+        <v>1877.41</v>
       </c>
     </row>
     <row r="19">
@@ -5921,7 +5743,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>35962.82</v>
+        <v>30250.79</v>
       </c>
     </row>
     <row r="21">
@@ -6003,13 +5825,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1135928.72</v>
+        <v>1054547.31</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1014291.81</v>
+        <v>998320.26</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -6022,16 +5844,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>8319.16</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>-1525.42</v>
+        <v>5042.01</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>71536.83</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>120111.49</v>
+        <v>127763.88</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>212904.51</v>
+        <v>204585.35</v>
       </c>
     </row>
     <row r="7">
@@ -6079,16 +5901,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
     </row>
     <row r="10">
@@ -6097,17 +5919,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>23.1</v>
+      <c r="B10" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>22.2</v>
       </c>
     </row>
     <row r="11">
@@ -6116,16 +5938,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="23" t="n">
+      <c r="B11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="n">
         <v>-2.49</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="21" t="n">
         <v>-9.41</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="21" t="n">
         <v>-9.470000000000001</v>
       </c>
     </row>
@@ -6170,13 +5992,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>566922.75</v>
+        <v>565614.48</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>574715.77</v>
+        <v>574597.67</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -6189,16 +6011,16 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>2820.25</v>
+        <v>3648.32</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>10415.63</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>2622.61</v>
+        <v>8903.65</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>-79.54000000000001</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>68006.44</v>
+        <v>65186.19</v>
       </c>
     </row>
     <row r="17">
@@ -6246,16 +6068,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>577338.38</v>
+        <v>574518.13</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>577338.38</v>
+        <v>574518.13</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>577338.38</v>
+        <v>574518.13</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>577338.38</v>
+        <v>574518.13</v>
       </c>
     </row>
     <row r="20">
@@ -6264,17 +6086,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E20" s="20" t="n">
-        <v>13.35</v>
+      <c r="B20" s="19" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>12.8</v>
       </c>
     </row>
     <row r="21">
@@ -6283,16 +6105,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="23" t="n">
+      <c r="B21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="21" t="n">
         <v>-2.79</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="21" t="n">
         <v>-9.57</v>
       </c>
     </row>
@@ -6337,13 +6159,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>569005.96</v>
+        <v>488932.83</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>439576.04</v>
+        <v>423722.59</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -6356,16 +6178,16 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>5498.91</v>
-      </c>
-      <c r="C26" s="19" t="n">
-        <v>-11941.04</v>
+        <v>1393.69</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>62633.18</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>117488.88</v>
+        <v>127843.42</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>144898.07</v>
+        <v>139399.16</v>
       </c>
     </row>
     <row r="27">
@@ -6413,16 +6235,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
     </row>
     <row r="30">
@@ -6431,17 +6253,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="21" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>26.73</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>35.16</v>
+      <c r="B30" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>33.82</v>
       </c>
     </row>
     <row r="31">
@@ -6450,16 +6272,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="23" t="n">
+      <c r="B31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="21" t="n">
         <v>-5.6</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="21" t="n">
         <v>-18.48</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="21" t="n">
         <v>-18.48</v>
       </c>
     </row>
@@ -6509,8 +6331,8 @@
           <t>Operating cash flow</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>-1525.42</v>
+      <c r="B4" s="4" t="n">
+        <v>71536.83</v>
       </c>
     </row>
     <row r="5">
@@ -6520,7 +6342,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>119477.79</v>
+        <v>23428.01</v>
       </c>
     </row>
     <row r="6">
@@ -6529,7 +6351,7 @@
           <t>Financing cash flow</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6540,7 +6362,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>117952.37</v>
+        <v>94964.84</v>
       </c>
     </row>
     <row r="8">
@@ -6550,7 +6372,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>196753.26</v>
+        <v>167616.4</v>
       </c>
     </row>
     <row r="9">
@@ -6560,7 +6382,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>338327.1</v>
+        <v>402427.78</v>
       </c>
     </row>
     <row r="11">
@@ -6584,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8178,16 +8000,6 @@
       </c>
       <c r="B160" s="4" t="n">
         <v>1126084.14</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B161" s="12" t="n">
-        <v>1134403.3</v>
       </c>
     </row>
   </sheetData>
@@ -8292,34 +8104,34 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1134403.3</v>
+        <v>1126084.14</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>788378.49</v>
+        <v>717305.58</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>384885.7</v>
+        <v>317539.23</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1173264.19</v>
+        <v>1034844.81</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>403492.79</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>1.034</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>103.43</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>51.71</v>
+        <v>399766.35</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>45.95</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -8329,34 +8141,34 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>577338.38</v>
+        <v>574518.13</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>148107.49</v>
+        <v>83185.75999999999</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>147463.95</v>
+        <v>80556.63</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>295571.44</v>
+        <v>163742.39</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>643.54</v>
+        <v>2629.13</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.512</v>
+        <v>0.285</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>51.2</v>
+        <v>28.5</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>25.6</v>
+        <v>14.25</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -8366,31 +8178,31 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>557064.92</v>
+        <v>551566.01</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>640271</v>
+        <v>634119.8199999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>237421.75</v>
+        <v>236982.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>877692.75</v>
+        <v>871102.42</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>402849.25</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>1.576</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>157.56</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>78.78</v>
+        <v>397137.22</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.579</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>78.97</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>5</v>
@@ -8410,7 +8222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8431,7 +8243,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.1506  ·  effective N pairs=6.6  ·  max pair=21.76% of gross</t>
+          <t>HHI=0.1751  ·  effective N pairs=5.7  ·  max pair=24.63% of gross</t>
         </is>
       </c>
     </row>
@@ -8479,11 +8291,11 @@
       <c r="C6" s="4" t="n">
         <v>183212.28</v>
       </c>
-      <c r="D6" s="22" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>15.62</v>
+      <c r="D6" s="20" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>17.7</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>1</v>
@@ -8496,16 +8308,16 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>173905.2</v>
+        <v>159949.1</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>173905.2</v>
-      </c>
-      <c r="D7" s="20" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>14.82</v>
+        <v>159949.1</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>15.46</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>1</v>
@@ -8514,20 +8326,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>100654.42</v>
+        <v>104270.18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>100654.42</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>8.58</v>
+        <v>104270.18</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>10.08</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>1</v>
@@ -8536,20 +8348,20 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>96465.25999999999</v>
+        <v>100654.42</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>96465.25999999999</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>8.220000000000001</v>
+        <v>100654.42</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>9.73</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>1</v>
@@ -8567,11 +8379,11 @@
       <c r="C10" s="4" t="n">
         <v>86033.84</v>
       </c>
-      <c r="D10" s="22" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>7.33</v>
+      <c r="D10" s="20" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>8.31</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>1</v>
@@ -8584,16 +8396,16 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>76298.25</v>
+        <v>83185.75999999999</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>76298.25</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>6.5</v>
+        <v>83185.75999999999</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>8.039999999999999</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -8602,20 +8414,20 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>74406.67</v>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>-74406.67</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>6.34</v>
+        <v>80556.63</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>-80556.63</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>7.78</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>1</v>
@@ -8624,20 +8436,20 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>73057.28</v>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>-73057.28</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>6.23</v>
+        <v>71643.42</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>-71643.42</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>6.92</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>1</v>
@@ -8646,20 +8458,20 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>72068.56</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>-72068.56</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>6.14</v>
+        <v>52191.35</v>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>-52191.35</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>5.04</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>1</v>
@@ -8668,27 +8480,27 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>71809.24000000001</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>71809.24000000001</v>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>6.12</v>
+        <v>50571.08</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>-50571.08</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>4.89</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>SECTOR NET EXPOSURE</t>
         </is>
@@ -8728,16 +8540,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>457771.9</v>
+        <v>443815.8</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>48594.36</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>409177.54</v>
+        <v>395221.44</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>34.88</v>
+        <v>38.19</v>
       </c>
     </row>
     <row r="21">
@@ -8747,16 +8559,16 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>76298.25</v>
+        <v>83185.75999999999</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>76298.25</v>
+        <v>83185.75999999999</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>6.5</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -8769,13 +8581,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>64567.48</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>-64567.48</v>
+        <v>64553.47</v>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>-64553.47</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-5.5</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="23">
@@ -8790,11 +8602,11 @@
       <c r="C23" s="12" t="n">
         <v>52191.35</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="29" t="n">
         <v>-52191.35</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-4.45</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="24">
@@ -8804,16 +8616,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>96465.25999999999</v>
+        <v>104270.18</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>73057.28</v>
+        <v>80556.63</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>23407.98</v>
+        <v>23713.55</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="25">
@@ -8826,32 +8638,13 @@
         <v>86033.84</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>72068.56</v>
+        <v>71643.42</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>13965.28</v>
+        <v>14390.42</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>71809.24000000001</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>74406.67</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>-2597.43</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>-0.22</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -8868,7 +8661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8889,7 +8682,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.978</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="4">
@@ -8898,8 +8691,8 @@
           <t>Gross beta</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>1.625</v>
+      <c r="B4" s="6" t="n">
+        <v>1.526</v>
       </c>
     </row>
     <row r="5">
@@ -8908,8 +8701,8 @@
           <t>Momentum factor net (% NAV)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>35.51</v>
+      <c r="B5" s="6" t="n">
+        <v>35.27</v>
       </c>
     </row>
     <row r="6">
@@ -8925,7 +8718,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>SECTOR NET VECTOR (% of gross)</t>
         </is>
@@ -8949,8 +8742,8 @@
           <t>tech</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
-        <v>34.88</v>
+      <c r="B10" s="20" t="n">
+        <v>38.19</v>
       </c>
     </row>
     <row r="11">
@@ -8959,8 +8752,8 @@
           <t>realestate</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>6.5</v>
+      <c r="B11" s="19" t="n">
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -8969,8 +8762,8 @@
           <t>health</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>-5.5</v>
+      <c r="B12" s="21" t="n">
+        <v>-6.24</v>
       </c>
     </row>
     <row r="13">
@@ -8979,8 +8772,8 @@
           <t>utilities</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
-        <v>-4.45</v>
+      <c r="B13" s="23" t="n">
+        <v>-5.04</v>
       </c>
     </row>
     <row r="14">
@@ -8989,8 +8782,8 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
-        <v>2</v>
+      <c r="B14" s="20" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="15">
@@ -8999,18 +8792,8 @@
           <t>industrial</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n">
-        <v>-0.22</v>
+      <c r="B15" s="19" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
